--- a/product_selector_out/STM32F3 series - diff.xlsx
+++ b/product_selector_out/STM32F3 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,6 +47,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
@@ -58,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E240"/>
+  <dimension ref="A1:E174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4250</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="18">
@@ -667,22 +667,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -694,70 +690,62 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F334C6</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F334C6</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -766,40 +754,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F334C6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10||9</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10, 9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -807,26 +799,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10||9 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -834,16 +826,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -853,63 +845,71 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>25 (workbook and API agree)</t>
+          <t>24||25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>24, 25</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>24||25 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -921,14 +921,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>24||25</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>10</t>
@@ -936,7 +932,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -948,70 +944,62 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>24, 25</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>24||25 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1020,21 +1008,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1043,88 +1031,76 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1138,7 +1114,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1147,7 +1123,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1161,7 +1137,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1170,25 +1146,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15||18</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -1197,25 +1173,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15, 18</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -1224,25 +1200,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>25 (workbook and API agree)</t>
+          <t>15||18 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -1251,53 +1227,61 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>37||38</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>37, 38</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1307,78 +1291,70 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>37||38 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1392,7 +1368,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1401,7 +1377,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1415,7 +1391,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1424,102 +1400,90 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1528,21 +1492,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1551,88 +1515,76 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>37||38</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>37, 38</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>37||38 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1646,7 +1598,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1655,7 +1607,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1669,7 +1621,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1678,7 +1630,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1692,7 +1644,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1701,7 +1653,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1715,7 +1667,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1724,7 +1676,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1738,7 +1690,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1747,7 +1699,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1761,7 +1713,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1770,7 +1722,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1784,7 +1736,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1793,7 +1745,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1807,7 +1759,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1816,7 +1768,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1830,7 +1782,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1839,7 +1791,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1853,7 +1805,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1862,7 +1814,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F301R8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1876,7 +1828,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1885,7 +1837,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F301R8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1899,7 +1851,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1908,7 +1860,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F301C8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1922,7 +1874,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1931,7 +1883,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F301C8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1945,7 +1897,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1954,90 +1906,102 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>8||9</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>8, 9</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>8||9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2046,21 +2010,21 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2069,21 +2033,21 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F301C6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2092,21 +2056,21 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F301C6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2115,21 +2079,21 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F301R6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2138,125 +2102,125 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F301R6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>8||9</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>51 (workbook and API agree)</t>
+          <t>8, 9</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>8||9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2265,88 +2229,76 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F302C6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2360,7 +2312,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2369,7 +2321,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F302C6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2383,7 +2335,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2392,7 +2344,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2406,7 +2358,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2415,7 +2367,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2429,7 +2381,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2438,102 +2390,90 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2542,21 +2482,21 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2565,88 +2505,76 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2660,7 +2588,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2669,7 +2597,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2683,7 +2611,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2692,7 +2620,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2706,7 +2634,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2715,7 +2643,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2729,7 +2657,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2738,7 +2666,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2752,7 +2680,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2761,7 +2689,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2775,7 +2703,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2784,102 +2712,90 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2888,21 +2804,21 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2911,88 +2827,76 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3006,7 +2910,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3015,7 +2919,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3029,7 +2933,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3038,102 +2942,90 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>24 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3142,21 +3034,21 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3165,88 +3057,76 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3260,7 +3140,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3269,7 +3149,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3283,7 +3163,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3292,7 +3172,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3306,7 +3186,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3315,7 +3195,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3329,7 +3209,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3338,102 +3218,90 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3442,21 +3310,21 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3465,88 +3333,76 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3560,7 +3416,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3569,7 +3425,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3583,7 +3439,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3592,102 +3448,90 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3696,21 +3540,21 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3719,21 +3563,21 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3742,21 +3586,21 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3765,21 +3609,21 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3788,21 +3632,21 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3811,21 +3655,21 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32F302VE</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3834,21 +3678,21 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32F302VE</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3857,21 +3701,21 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3880,21 +3724,21 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3903,88 +3747,76 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3998,7 +3830,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4007,7 +3839,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4021,7 +3853,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4030,7 +3862,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4044,7 +3876,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4053,7 +3885,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4067,7 +3899,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4076,102 +3908,90 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>24 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4180,21 +4000,21 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4203,21 +4023,21 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4226,21 +4046,21 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4249,88 +4069,76 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F373CB</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F373CB</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E166" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F373RC</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4344,7 +4152,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4353,7 +4161,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F373RC</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4367,7 +4175,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4376,102 +4184,90 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F373CC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F373CC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F373RB</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F373RB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4480,21 +4276,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F373VB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4503,1606 +4299,28 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F373VB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>STM32F303RD</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>STM32F303RD</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>STM32F303RD</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>STM32F303RD</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>STM32F303RD</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>STM32F303RD</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>STM32F303RD</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>STM32F303VD</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>STM32F303VD</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>STM32F303K8</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E184" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>STM32F303K8</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E185" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>STM32F303VC</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>STM32F303VC</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E187" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>STM32F303C8</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>STM32F303C8</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E189" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>STM32F303RC</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E190" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>STM32F303RC</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>STM32F303CC</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E192" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>STM32F303CC</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E193" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>STM32F303CB</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>STM32F303CB</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E195" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>STM32F303VE</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E196" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>STM32F303VE</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E197" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>STM32F303RB</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E198" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>STM32F303RB</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>STM32F303R6</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E200" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>STM32F303R6</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E201" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>STM32F303VB</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E202" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>STM32F303VB</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>STM32F303K6</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E204" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>STM32F303K6</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E205" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>STM32F303C6</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E206" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>STM32F303C6</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E207" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E211" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E215" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E218" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E219" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E220" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>STM32F303R8</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E221" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>STM32F303R8</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E222" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>STM32F373C8</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E223" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>STM32F373C8</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E224" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>STM32F373R8</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E225" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>STM32F373R8</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>STM32F373V8</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E227" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>STM32F373V8</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E228" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>STM32F373VC</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>STM32F373VC</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E230" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>STM32F373CB</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E231" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>STM32F373CB</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E232" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>STM32F373RC</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E233" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>STM32F373RC</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E234" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>STM32F373CC</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E235" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>STM32F373CC</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E236" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>STM32F373RB</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E237" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>STM32F373RB</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E238" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>STM32F373VB</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E239" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>STM32F373VB</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E240" s="6" t="inlineStr">
-        <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E240"/>
+  <autoFilter ref="A18:E174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F3 series - diff.xlsx
+++ b/product_selector_out/STM32F3 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,11 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -91,6 +96,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -559,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -629,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4272</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="18">
@@ -759,22 +765,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>10||9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -786,137 +788,117 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>10, 9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>10||9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>24||25</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>24, 25</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>24||25 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -939,7 +921,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -962,7 +944,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -985,7 +967,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1008,138 +990,162 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15||18</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15, 18</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>15||18 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>37||38</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>37, 38</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>37||38 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1151,22 +1157,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>15||18</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1178,137 +1180,117 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>15, 18</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>15||18 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>37||38</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>37, 38</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>37||38 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1331,7 +1313,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1354,7 +1336,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1377,7 +1359,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1400,7 +1382,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1423,7 +1405,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1446,7 +1428,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1469,7 +1451,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1492,7 +1474,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1515,7 +1497,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1538,7 +1520,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1561,7 +1543,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1584,7 +1566,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1607,7 +1589,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1630,7 +1612,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1653,7 +1635,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1676,7 +1658,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F301R8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1699,7 +1681,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F301R8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1722,7 +1704,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F301C8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1745,7 +1727,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F301C8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1768,87 +1750,99 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>8||9</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>8, 9</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8||9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -1860,18 +1854,18 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -1883,18 +1877,18 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F301C6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -1906,168 +1900,168 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F301C6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>8||9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F301R6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>8, 9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F301R6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>8||9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>8||9</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>8, 9</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>8||9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2079,18 +2073,18 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2102,18 +2096,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2125,88 +2119,76 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>8||9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302C6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>8, 9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302C6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>8||9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2229,7 +2211,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2252,7 +2234,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2275,7 +2257,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2298,7 +2280,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2321,7 +2303,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2344,7 +2326,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2367,7 +2349,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2390,7 +2372,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2413,7 +2395,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2436,7 +2418,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2459,7 +2441,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2482,7 +2464,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2505,7 +2487,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2528,7 +2510,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2551,7 +2533,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2574,7 +2556,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2597,7 +2579,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2620,7 +2602,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2643,7 +2625,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2666,7 +2648,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2689,7 +2671,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2712,7 +2694,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2735,7 +2717,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2758,7 +2740,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F302VE</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2781,7 +2763,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F302VE</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2804,7 +2786,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2827,7 +2809,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2850,7 +2832,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2873,7 +2855,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2896,7 +2878,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2919,7 +2901,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2942,7 +2924,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2965,7 +2947,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2988,7 +2970,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3011,7 +2993,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3034,7 +3016,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3057,7 +3039,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3080,7 +3062,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3103,7 +3085,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3126,7 +3108,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3149,7 +3131,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3172,7 +3154,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3195,7 +3177,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3218,7 +3200,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3241,7 +3223,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3264,7 +3246,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3287,7 +3269,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3310,7 +3292,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3333,7 +3315,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3356,7 +3338,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3379,7 +3361,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3402,7 +3384,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3425,7 +3407,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3448,99 +3430,115 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3563,7 +3561,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3586,7 +3584,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3609,7 +3607,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3632,7 +3630,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3655,7 +3653,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3678,7 +3676,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3701,7 +3699,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3724,7 +3722,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3747,7 +3745,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3770,7 +3768,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3793,7 +3791,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3816,46 +3814,54 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3867,18 +3873,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3890,25 +3900,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32F373C8</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3931,7 +3945,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32F373C8</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3954,7 +3968,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32F373R8</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3977,7 +3991,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32F373R8</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4000,7 +4014,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32F373V8</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4023,7 +4037,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32F373V8</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4046,7 +4060,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32F373VC</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4069,7 +4083,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32F373VC</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4092,7 +4106,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32F373CB</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4115,7 +4129,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32F373CB</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4138,7 +4152,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32F373RC</t>
+          <t>STM32F373CB</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4161,7 +4175,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32F373RC</t>
+          <t>STM32F373CB</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4184,7 +4198,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32F373CC</t>
+          <t>STM32F373RC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4207,7 +4221,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32F373CC</t>
+          <t>STM32F373RC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4230,7 +4244,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32F373RB</t>
+          <t>STM32F373CC</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4253,7 +4267,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32F373RB</t>
+          <t>STM32F373CC</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4276,7 +4290,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32F373VB</t>
+          <t>STM32F373RB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4299,7 +4313,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32F373VB</t>
+          <t>STM32F373RB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4319,8 +4333,54 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>STM32F373VB</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>STM32F373VB</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E174"/>
+  <autoFilter ref="A18:E176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F3 series - diff.xlsx
+++ b/product_selector_out/STM32F3 series - diff.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4416</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4270</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="18">
